--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_130_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_130_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.581</v>
+        <v>3.2772</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2328</v>
+        <v>3.761</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6518</v>
+        <v>-0.4838</v>
       </c>
       <c r="G2" t="n">
         <v>1.7677</v>
@@ -610,13 +610,13 @@
         <v>0.4639</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2772</v>
+        <v>-0.0266</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3462</v>
+        <v>-0.1256</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8568</v>
+        <v>2.5713</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5431</v>
+        <v>2.0896</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3137</v>
+        <v>0.4818</v>
       </c>
       <c r="G3" t="n">
         <v>1.8116</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.168</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5975</v>
+        <v>-0.051</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1823</v>
+        <v>0.0479</v>
       </c>
       <c r="E4" t="n">
-        <v>1.496</v>
+        <v>1.3993</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3137</v>
+        <v>-1.3515</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9742</v>
+        <v>-0.6379</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-3.4117</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2408</v>
+        <v>2.7738</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4847</v>
+        <v>1.9109</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6687</v>
+        <v>-1.4985</v>
       </c>
       <c r="L4" t="n">
-        <v>0.184</v>
+        <v>3.4094</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4895</v>
+        <v>-2.5488</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-1.9132</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4248</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9968</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9085</v>
+        <v>-0.5658</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0883</v>
+        <v>-0.3541</v>
       </c>
       <c r="V4" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.214</v>
+      </c>
+      <c r="X4" t="n">
         <v>-0.5361</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.6083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2298</v>
+        <v>-0.4006</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8528</v>
+        <v>0.745</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0826</v>
+        <v>-1.1456</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6379</v>
+        <v>-0.9742</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.4117</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7738</v>
+        <v>-0.2408</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9109</v>
+        <v>-0.4847</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4985</v>
+        <v>-0.6687</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4094</v>
+        <v>0.184</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5488</v>
+        <v>-0.4895</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9132</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.4248</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1975</v>
+        <v>0.4138</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1123</v>
+        <v>0.1575</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0852</v>
+        <v>0.2563</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4626</v>
+        <v>-0.6636</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1453</v>
+        <v>4.3812</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.608</v>
+        <v>-5.0448</v>
       </c>
       <c r="G6" t="n">
         <v>1.0305</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7947</v>
+        <v>-0.9957</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8136</v>
+        <v>-0.5777</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0189</v>
+        <v>-0.418</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9304</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7471</v>
+        <v>-1.1853</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1504</v>
+        <v>-0.6222</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5967</v>
+        <v>-0.5631</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4812</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2702</v>
+        <v>-0.168</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8087</v>
+        <v>-1.3011</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0473</v>
+        <v>-0.9388</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7614</v>
+        <v>-0.3622</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4668</v>
+        <v>1.3683</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4731</v>
+        <v>-1.0543</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9937</v>
+        <v>2.4226</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.442</v>
+        <v>3.2163</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7661</v>
+        <v>0.0511</v>
       </c>
       <c r="L8" t="n">
+        <v>3.1652</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.848</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1.1053</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.7426</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.8556</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.4793</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.6237</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.8138</v>
+      </c>
+      <c r="T8" t="n">
         <v>-0.6758999999999999</v>
       </c>
-      <c r="M8" t="n">
-        <v>-0.0248</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.3178</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.0378</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.1415</v>
-      </c>
       <c r="U8" t="n">
-        <v>0.1037</v>
+        <v>-0.1379</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.864</v>
+        <v>-1.7415</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3674</v>
+        <v>-1.0473</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4967</v>
+        <v>-0.6942</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3683</v>
+        <v>-1.4668</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0543</v>
+        <v>-0.4731</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4226</v>
+        <v>-0.9937</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2163</v>
+        <v>-1.442</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0511</v>
+        <v>-0.7661</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1652</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.848</v>
+        <v>-0.0248</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1053</v>
+        <v>0.293</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7426</v>
+        <v>-0.3178</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3768</v>
+        <v>0.0294</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1044</v>
+        <v>-0.1415</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2724</v>
+        <v>0.1709</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8602</v>
+        <v>-4.341</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7869</v>
+        <v>-2.0661</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0733</v>
+        <v>-2.275</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0245</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5316</v>
+        <v>-1.0124</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2513</v>
+        <v>-0.5305</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2803</v>
+        <v>-0.4819</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0413</v>
+        <v>-4.4351</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8675</v>
+        <v>-1.3957</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1738</v>
+        <v>-3.0394</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8243</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9129</v>
+        <v>-0.3066</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>-0.3497</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0914</v>
+        <v>0.0431</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.931</v>
+        <v>-7.7794</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2716</v>
+        <v>-2.1537</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.6593</v>
+        <v>-5.6257</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8762</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8228</v>
+        <v>-0.6713</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4323</v>
+        <v>-0.3143</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3905</v>
+        <v>-0.3569</v>
       </c>
       <c r="V12" t="n">
         <v>-3.2166</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.3246</v>
+        <v>-15.9512</v>
       </c>
       <c r="E13" t="n">
-        <v>3.778900000000001</v>
+        <v>4.152299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.1036</v>
+        <v>-20.1035</v>
       </c>
       <c r="G13" t="n">
         <v>-2.307</v>
@@ -1468,13 +1468,13 @@
         <v>11.5978</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.0125</v>
+        <v>-4.6391</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.4574</v>
+        <v>-3.084</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5551</v>
+        <v>-1.555</v>
       </c>
       <c r="V13" t="n">
         <v>-6.685700000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.2606</v>
+        <v>10.7615</v>
       </c>
       <c r="E14" t="n">
-        <v>10.827</v>
+        <v>10.4732</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4336</v>
+        <v>0.2884</v>
       </c>
       <c r="G14" t="n">
         <v>5.4884</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7875</v>
+        <v>1.2885</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9085</v>
+        <v>0.5546</v>
       </c>
       <c r="U14" t="n">
-        <v>0.879</v>
+        <v>0.7339</v>
       </c>
       <c r="V14" t="n">
         <v>3.7527</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5358</v>
+        <v>4.6322</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3004</v>
+        <v>2.4184</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2353</v>
+        <v>2.2138</v>
       </c>
       <c r="G15" t="n">
         <v>1.2428</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2028</v>
+        <v>1.2992</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5034</v>
+        <v>0.6214</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6994</v>
+        <v>0.6778</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8709</v>
+        <v>3.0784</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8414</v>
+        <v>3.1206</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9704</v>
+        <v>-0.0422</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3542</v>
+        <v>-2.2407</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4261</v>
+        <v>-1.3073</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7803</v>
+        <v>-0.9334</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4923</v>
+        <v>-0.8682</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3431</v>
+        <v>-1.1995</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1492</v>
+        <v>0.3312</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1381</v>
+        <v>-1.3725</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7692</v>
+        <v>-0.1078</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3688</v>
+        <v>-1.2647</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4266</v>
+        <v>0.3165</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>0.2361</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4538</v>
+        <v>0.0804</v>
       </c>
       <c r="V16" t="n">
+        <v>3.6109</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.7527</v>
+      </c>
+      <c r="X16" t="n">
         <v>-0.1418</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8374</v>
+        <v>2.7422</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2385</v>
+        <v>4.7234</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4011</v>
+        <v>-1.9812</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2407</v>
+        <v>2.3542</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3073</v>
+        <v>-0.4261</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9334</v>
+        <v>2.7803</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8682</v>
+        <v>5.4923</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1995</v>
+        <v>0.3431</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3312</v>
+        <v>5.1492</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3725</v>
+        <v>-3.1381</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1078</v>
+        <v>-0.7692</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2647</v>
+        <v>-2.3688</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0756</v>
+        <v>0.2978</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3541</v>
+        <v>-0.1452</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2785</v>
+        <v>0.443</v>
       </c>
       <c r="V17" t="n">
-        <v>3.6109</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7527</v>
+        <v>0.5361</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3409</v>
+        <v>1.3574</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9276</v>
+        <v>2.8097</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5867</v>
+        <v>-1.4523</v>
       </c>
       <c r="G18" t="n">
         <v>0.2251</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.188</v>
+        <v>0.2045</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1221</v>
+        <v>0.0042</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0659</v>
+        <v>0.2003</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4808</v>
+        <v>1.0757</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7165</v>
+        <v>1.9524</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2356</v>
+        <v>-0.8767</v>
       </c>
       <c r="G19" t="n">
         <v>-0.976</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4709</v>
+        <v>0.1239</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>-0.503</v>
       </c>
       <c r="U19" t="n">
-        <v>0.268</v>
+        <v>0.6269</v>
       </c>
       <c r="V19" t="n">
         <v>0.5361</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8057</v>
+        <v>0.0353</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8435</v>
+        <v>0.0635</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0378</v>
+        <v>-0.0282</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.28</v>
+        <v>0.8776</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0216</v>
+        <v>2.9386</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3016</v>
+        <v>-2.0611</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0315</v>
+        <v>1.5455</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9614</v>
+        <v>2.1846</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0701</v>
+        <v>-0.6391</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3115</v>
+        <v>-0.6679</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0602</v>
+        <v>0.754</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3717</v>
+        <v>-1.422</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4743</v>
+        <v>0.6939</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9085</v>
+        <v>0.1417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5658</v>
+        <v>0.5522</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9133</v>
+        <v>-0.8282</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5262</v>
+        <v>-1.7834</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3871</v>
+        <v>0.9552</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8776</v>
+        <v>-2.689</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9386</v>
+        <v>-1.7154</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0611</v>
+        <v>-0.9736</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5455</v>
+        <v>-0.8522</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1846</v>
+        <v>-2.0902</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6391</v>
+        <v>1.2379</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6679</v>
+        <v>-1.8368</v>
       </c>
       <c r="N22" t="n">
-        <v>0.754</v>
+        <v>0.3748</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.422</v>
+        <v>-2.2116</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.6237</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2548</v>
+        <v>1.2551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>0.5507</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1933</v>
+        <v>0.7044</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.373</v>
+        <v>-1.0809</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1373</v>
+        <v>-1.4332</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7643</v>
+        <v>0.3523</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.689</v>
+        <v>-0.28</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7154</v>
+        <v>1.0216</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9736</v>
+        <v>-1.3016</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8522</v>
+        <v>1.0315</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0902</v>
+        <v>0.9614</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2379</v>
+        <v>0.0701</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8368</v>
+        <v>-1.3115</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3748</v>
+        <v>0.0602</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2116</v>
+        <v>-1.3717</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7103</v>
+        <v>1.1991</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1968</v>
+        <v>0.3187</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5135</v>
+        <v>0.8804</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1417</v>
+        <v>-4.1081</v>
       </c>
       <c r="E24" t="n">
         <v>-3.3131</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8286</v>
+        <v>-0.795</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6953</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.127</v>
+        <v>-0.0934</v>
       </c>
       <c r="T24" t="n">
         <v>-0.224</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>16.3247</v>
+        <v>17.8975</v>
       </c>
       <c r="E25" t="n">
-        <v>19.0313</v>
+        <v>19.0315</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.706500000000001</v>
+        <v>-1.133899999999999</v>
       </c>
       <c r="G25" t="n">
         <v>2.307100000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>8.079000000000001</v>
+        <v>8.079000000000002</v>
       </c>
       <c r="I25" t="n">
         <v>-5.772</v>
@@ -2383,7 +2383,7 @@
         <v>7.3687</v>
       </c>
       <c r="L25" t="n">
-        <v>9.769099999999998</v>
+        <v>9.7691</v>
       </c>
       <c r="M25" t="n">
         <v>-14.8308</v>
@@ -2395,7 +2395,7 @@
         <v>-15.5412</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3197</v>
+        <v>2.319699999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-11.5977</v>
@@ -2404,13 +2404,13 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>5.0124</v>
+        <v>6.5851</v>
       </c>
       <c r="T25" t="n">
         <v>1.5552</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4573</v>
+        <v>5.029999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>6.685700000000001</v>
